--- a/data/trans_orig/Q20A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q20A-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que ha estado hospitalizado en los últimos 12 meses</t>
+          <t>Número medio de veces que la población ha estado hospitalizada en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,32 +721,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,77</t>
+          <t>0,09; 0,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,34</t>
+          <t>0,04; 0,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,06</t>
+          <t>0,02; 0,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,09</t>
+          <t>0,03; 0,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,41</t>
+          <t>0,16; 0,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,34</t>
+          <t>0,13; 0,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,07</t>
+          <t>0,03; 0,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,52</t>
+          <t>0,14; 0,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,26</t>
+          <t>0,1; 0,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -861,39 +861,39 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,15</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0,03; 0,09</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,1; 0,19</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,11</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0,04; 0,09</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,14</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,14</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 0,19</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,11</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,03; 0,08</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0,07; 0,12</t>
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,16</t>
+          <t>0,1; 0,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,13</t>
+          <t>0,05; 0,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,07</t>
+          <t>0,02; 0,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,13</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,08</t>
+          <t>0,03; 0,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,15</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,1</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,2</t>
+          <t>0,02; 0,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,15</t>
+          <t>0,06; 0,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,64</t>
+          <t>0,06; 0,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,19</t>
+          <t>0,05; 0,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,17 +1166,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,13</t>
+          <t>0,06; 0,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,12</t>
+          <t>0,04; 0,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,15</t>
+          <t>0,04; 0,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,26</t>
+          <t>0,06; 0,27</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,13</t>
+          <t>0,03; 0,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,05</t>
+          <t>0,01; 0,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,17</t>
+          <t>0,07; 0,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,06</t>
+          <t>0,02; 0,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,17</t>
+          <t>0,07; 0,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,13</t>
+          <t>0,07; 0,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,17</t>
+          <t>0,05; 0,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,22</t>
+          <t>0,1; 0,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1446,14 +1446,14 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>0,08; 0,2</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>0,08; 0,19</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,19</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
           <t>0,07; 0,14</t>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,16</t>
+          <t>0,09; 0,15</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,08</t>
+          <t>0,04; 0,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,31</t>
+          <t>0,06; 0,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,17</t>
+          <t>0,08; 0,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,05; 0,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,11</t>
+          <t>0,06; 0,1</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1841,27 +1841,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,13</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,08</t>
+          <t>0,05; 0,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,11</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,12</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,13</t>
+          <t>0,1; 0,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">

--- a/data/trans_orig/Q20A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q20A-Provincia-trans_orig.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,06</t>
         </is>
       </c>
     </row>
@@ -716,37 +716,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,09</t>
+          <t>0,03; 0,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,87</t>
+          <t>0,09; 0,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,32</t>
+          <t>0,05; 0,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,07</t>
+          <t>0,02; 0,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,09</t>
+          <t>0,02; 0,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,38</t>
+          <t>0,15; 0,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,32</t>
+          <t>0,13; 0,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,55</t>
+          <t>0,15; 0,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,27</t>
+          <t>0,1; 0,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,14</t>
+          <t>0,05; 0,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,14</t>
+          <t>0,07; 0,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,14</t>
+          <t>0,07; 0,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,13</t>
+          <t>0,08; 0,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,19</t>
+          <t>0,1; 0,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,09</t>
+          <t>0,04; 0,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1001,22 +1001,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,14</t>
+          <t>0,05; 0,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,08</t>
+          <t>0,02; 0,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,06; 0,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,07</t>
+          <t>0,03; 0,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,09</t>
+          <t>0,03; 0,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,05; 0,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1103,14 +1103,14 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>0,08</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,13</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,19</t>
+          <t>0,02; 0,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,15</t>
+          <t>0,07; 0,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,54</t>
+          <t>0,06; 0,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,21</t>
+          <t>0,06; 0,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,11</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,14</t>
+          <t>0,04; 0,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,27</t>
+          <t>0,08; 0,33</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,11</t>
+          <t>0,03; 0,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,06</t>
+          <t>0,01; 0,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,07; 0,17</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,03; 0,12</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0,03; 0,06</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>0,07; 0,16</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,03; 0,11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,02; 0,06</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,18</t>
-        </is>
-      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,13</t>
+          <t>0,06; 0,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,1</t>
+          <t>0,04; 0,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,21</t>
+          <t>0,1; 0,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,17</t>
+          <t>0,08; 0,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,2</t>
+          <t>0,08; 0,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,15</t>
+          <t>0,08; 0,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1523,19 +1523,19 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0,08</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
           <t>0,07</t>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,28</t>
+          <t>0,07; 0,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,06; 0,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,11</t>
+          <t>0,09; 0,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,15</t>
+          <t>0,09; 0,19</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,11</t>
+          <t>0,05; 0,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1711,47 +1711,47 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,05</t>
+          <t>0,03; 0,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,17</t>
+          <t>0,07; 0,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,07; 0,11</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0,03; 0,06</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>0,06; 0,11</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0,06; 0,1</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,08</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,03; 0,06</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,11</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,1</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,08</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,02; 0,05</t>
         </is>
       </c>
     </row>
@@ -1783,27 +1783,27 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0,08</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,09</t>
+          <t>0,05; 0,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,07; 0,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,12</t>
+          <t>0,09; 0,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,08</t>
+          <t>0,07; 0,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,09</t>
+          <t>0,07; 0,1</t>
         </is>
       </c>
     </row>
